--- a/data/Crop Efficiency - Stat Cards.xlsx
+++ b/data/Crop Efficiency - Stat Cards.xlsx
@@ -459,6 +459,12 @@
           <t>owned &amp; rented</t>
         </is>
       </c>
+      <c r="C2" t="n">
+        <v>2500</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2500</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">

--- a/data/Crop Efficiency - Stat Cards.xlsx
+++ b/data/Crop Efficiency - Stat Cards.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -502,6 +502,18 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Wheat/Rye Yield</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>bu/acre, vs. MI avg</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Crop Efficiency - Stat Cards.xlsx
+++ b/data/Crop Efficiency - Stat Cards.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -477,17 +477,23 @@
           <t>tons/acre, vs. MI avg</t>
         </is>
       </c>
+      <c r="C3" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Alfalfa Yield</t>
+          <t>Alfalfa Silage Yield</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
           <t>tons/acre, vs. MI avg</t>
         </is>
+      </c>
+      <c r="C4" t="n">
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -513,7 +519,11 @@
           <t>bu/acre, vs. MI avg</t>
         </is>
       </c>
+      <c r="C6" t="n">
+        <v>60</v>
+      </c>
     </row>
+    <row r="7"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Crop Efficiency - Stat Cards.xlsx
+++ b/data/Crop Efficiency - Stat Cards.xlsx
@@ -523,7 +523,21 @@
         <v>60</v>
       </c>
     </row>
-    <row r="7"/>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Total Value of Crops Produced</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>wheat + alfalfa only, excl. corn silage</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1413060</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
